--- a/forms/trg/Formulir_TRG_torcg.xlsx
+++ b/forms/trg/Formulir_TRG_torcg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B32)</f>
+        <f>COUNTA(Anggota!B5:B33)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F32)</f>
+        <f>COUNTA(Anggota!F5:F33)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ir. Rinaldi Sjahril, M.Agr. Ph.D.</t>
+          <t>Prof. Dr. Ir. Elkwakib Syam’un, M.P</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Horticulture</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +937,13 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8645-4828</t>
+          <t>0000-0001-5875-118X</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/12902658000</t>
+          <t>https://www.scopus.com/pages/authors/57202479859</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Katriani Mantja, M.P.</t>
+          <t>Prof. Ir. Rinaldi Sjahril, M.Agr. Ph.D.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Horticulture</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,11 +982,15 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6522-1689</t>
+          <t>0000-0001-8645-4828</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/authors/12902658000</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Rahmansyah Dermawan, S.P., M.P</t>
+          <t>Dr. Ir. Katriani Mantja, M.P.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1023,7 +1027,7 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4206-5673</t>
+          <t>0000-0001-6522-1689</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
@@ -1040,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Fachirah Ulfa, M.P</t>
+          <t>Dr. Rahmansyah Dermawan, S.P., M.P</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1064,7 +1068,7 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1736-9563</t>
+          <t>0000-0003-4206-5673</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
@@ -1081,12 +1085,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Feranita, M.P</t>
+          <t>Prof. Dr. Ir. Fachirah Ulfa, M.P</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>In Vitro Propagation</t>
+          <t>Horticulture</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1105,7 +1109,7 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2819-8456</t>
+          <t>0000-0002-1736-9563</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
@@ -1122,12 +1126,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muh. Faried, S.P., M.Si</t>
+          <t>Prof. Dr. Ir. Feranita, M.P</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Olericulture</t>
+          <t>In Vitro Propagation</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1146,15 +1150,11 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6326-1724</t>
+          <t>0000-0002-2819-8456</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>https://www.scopus.com/pages/authors/59189138200</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1167,22 +1167,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Jose Luis Trevizan Chiomento</t>
+          <t>Muh. Faried, S.P., M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>University of Passo Fundo, Brazil</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Horticulture</t>
+          <t>Olericulture</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1191,13 +1191,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>https://www.orcid.org/0000000348192761</t>
+          <t>0000-0001-6326-1724</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57192691478</t>
+          <t>https://www.scopus.com/pages/authors/59189138200</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1212,31 +1212,39 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Professor Tomonari Hirano</t>
+          <t>Prof. Dr. Jose Luis Trevizan Chiomento</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>University of Miyazaki</t>
+          <t>University of Passo Fundo, Brazil</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Plant Biotechnology</t>
+          <t>Horticulture</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>https://www.orcid.org/0000000348192761</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>57192691478</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1249,22 +1257,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Milawati Lalla, S.P., M.P.</t>
+          <t>Assoc. Professor Tomonari Hirano</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>University of Miyazaki</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Horticulture</t>
+          <t>Plant Biotechnology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1286,39 +1294,31 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Cennawati, S.P., M.Si</t>
+          <t>Dr. Milawati Lalla, S.P., M.P.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Muhmmadiyah Enrekang University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Horticulture Microbes</t>
+          <t>Horticulture</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-4949-4016</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>59198422100</t>
-        </is>
-      </c>
+      <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1331,22 +1331,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Padil Wijaya, S.Tr.P., M.Si.</t>
+          <t>Cennawati, S.P., M.Si</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Lambung Mangkurat University</t>
+          <t>Muhmmadiyah Enrekang University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Horticulture</t>
+          <t>Horticulture Microbes</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1355,13 +1355,13 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>my-orcid?orcid=0009-0003-0604-4100</t>
+          <t>0000-0003-4949-4016</t>
         </is>
       </c>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>59198774000</t>
+          <t>59198422100</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Abdul Jalil, S.P., M.Si.</t>
+          <t>Padil Wijaya, S.Tr.P., M.Si.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>UPTD BPPSDMP DPTPH Province Kalimantan Timur</t>
+          <t>Lambung Mangkurat University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1400,11 +1400,15 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-5435-0717</t>
+          <t>my-orcid?orcid=0009-0003-0604-4100</t>
         </is>
       </c>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>59198774000</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1417,17 +1421,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Remi Widana Putri, S.P., M.Si</t>
+          <t>Abdul Jalil, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>West Sulawesi University</t>
+          <t>UPTD BPPSDMP DPTPH Province Kalimantan Timur</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -1439,13 +1443,13 @@
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-5435-0717</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>58713999700</t>
-        </is>
-      </c>
+      <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1458,17 +1462,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Denisya Azyahra S.P</t>
+          <t>Remi Widana Putri, S.P., M.Si</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>West Sulawesi University</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1482,7 +1486,11 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>58713999700</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1495,12 +1503,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Cici Nur Maghfirah S.P</t>
+          <t>Denisya Azyahra S.P</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1532,33 +1540,29 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Masrinda Oktavia, S.P</t>
+          <t>Cici Nur Maghfirah S.P</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
           <t>Horticulture</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Trophort Team</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>0009-0009-0865-4037</t>
-        </is>
-      </c>
+      <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="11" t="inlineStr">
@@ -1571,18 +1575,42 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Masrinda Oktavia, S.P</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Horticulture</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Trophort Team</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-0865-4037</t>
+        </is>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1771,15 +1799,32 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="12" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
